--- a/results/data_availability/glioma_drug_data_availability.xlsx
+++ b/results/data_availability/glioma_drug_data_availability.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>DEPMAP_RECURRENCE_SCORE</t>
   </si>
@@ -654,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1652,56 +1652,56 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46">
-        <v>-0.2044527457271464</v>
+        <v>-0.2238031966272546</v>
       </c>
       <c r="C46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B47">
-        <v>-0.2238031966272546</v>
+        <v>-0.23305753079414</v>
       </c>
       <c r="C47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B48">
-        <v>-0.23305753079414</v>
+        <v>-0.2502889738691192</v>
       </c>
       <c r="C48" t="b">
         <v>0</v>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B49">
-        <v>-0.2502889738691192</v>
+        <v>-0.2141760698400222</v>
       </c>
       <c r="C49" t="b">
         <v>0</v>
@@ -1744,16 +1744,13 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>54</v>
-      </c>
-      <c r="B50">
-        <v>-0.2141760698400222</v>
+        <v>55</v>
       </c>
       <c r="C50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
@@ -1767,13 +1764,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="B51">
+        <v>-0.2175007508132131</v>
       </c>
       <c r="C51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -1787,10 +1787,10 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B52">
-        <v>-0.2175007508132131</v>
+        <v>-0.1753274481903328</v>
       </c>
       <c r="C52" t="b">
         <v>0</v>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B53">
-        <v>-0.2108562151939837</v>
+        <v>-0.2331316047101898</v>
       </c>
       <c r="C53" t="b">
         <v>0</v>
@@ -1828,15 +1828,15 @@
         <v>0</v>
       </c>
       <c r="G53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B54">
-        <v>-0.1753274481903328</v>
+        <v>-0.2522460594059376</v>
       </c>
       <c r="C54" t="b">
         <v>0</v>
@@ -1851,21 +1851,18 @@
         <v>0</v>
       </c>
       <c r="G54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>58</v>
-      </c>
-      <c r="B55">
-        <v>-0.2331316047101898</v>
+        <v>60</v>
       </c>
       <c r="C55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -1874,21 +1871,18 @@
         <v>0</v>
       </c>
       <c r="G55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>59</v>
-      </c>
-      <c r="B56">
-        <v>-0.2522460594059376</v>
+        <v>61</v>
       </c>
       <c r="C56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
@@ -1897,32 +1891,35 @@
         <v>0</v>
       </c>
       <c r="G56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="B57">
+        <v>-0.2152350766343056</v>
       </c>
       <c r="C57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C58" t="b">
         <v>1</v>
@@ -1942,30 +1939,30 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>62</v>
-      </c>
-      <c r="B59">
-        <v>-0.2152350766343056</v>
+        <v>64</v>
       </c>
       <c r="C59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="B60">
+        <v>-0.1981459608277116</v>
       </c>
       <c r="C60" t="b">
         <v>1</v>
@@ -1974,10 +1971,10 @@
         <v>1</v>
       </c>
       <c r="E60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="b">
         <v>0</v>
@@ -1985,13 +1982,16 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>66</v>
+      </c>
+      <c r="B61">
+        <v>-0.1818185487459437</v>
       </c>
       <c r="C61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
@@ -2005,22 +2005,22 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B62">
-        <v>-0.1981459608277116</v>
+        <v>-0.1904426883724705</v>
       </c>
       <c r="C62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="b">
         <v>0</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B63">
-        <v>-0.1818185487459437</v>
+        <v>-0.1957764448950246</v>
       </c>
       <c r="C63" t="b">
         <v>0</v>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B64">
-        <v>-0.1904426883724705</v>
+        <v>-0.2113764247837917</v>
       </c>
       <c r="C64" t="b">
         <v>0</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B65">
-        <v>-0.1957764448950246</v>
+        <v>-0.1866591968554417</v>
       </c>
       <c r="C65" t="b">
         <v>0</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B66">
-        <v>-0.2113764247837917</v>
+        <v>-0.1946857278803238</v>
       </c>
       <c r="C66" t="b">
         <v>0</v>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B67">
-        <v>-0.1866591968554417</v>
+        <v>-0.2501098993540255</v>
       </c>
       <c r="C67" t="b">
         <v>0</v>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B68">
-        <v>-0.1946857278803238</v>
+        <v>-0.1288493580431803</v>
       </c>
       <c r="C68" t="b">
         <v>0</v>
@@ -2166,56 +2166,56 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B69">
-        <v>-0.2501098993540255</v>
+        <v>-0.2357862821744499</v>
       </c>
       <c r="C69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B70">
-        <v>-0.1288493580431803</v>
+        <v>-0.226134911817538</v>
       </c>
       <c r="C70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B71">
-        <v>-0.2357862821744499</v>
+        <v>-0.1780704415155684</v>
       </c>
       <c r="C71" t="b">
         <v>1</v>
@@ -2230,15 +2230,15 @@
         <v>1</v>
       </c>
       <c r="G71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B72">
-        <v>-0.226134911817538</v>
+        <v>-0.1927359246324966</v>
       </c>
       <c r="C72" t="b">
         <v>1</v>
@@ -2258,10 +2258,7 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>76</v>
-      </c>
-      <c r="B73">
-        <v>-0.1780704415155684</v>
+        <v>78</v>
       </c>
       <c r="C73" t="b">
         <v>1</v>
@@ -2270,10 +2267,10 @@
         <v>1</v>
       </c>
       <c r="E73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" t="b">
         <v>0</v>
@@ -2281,30 +2278,30 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>77</v>
-      </c>
-      <c r="B74">
-        <v>-0.1927359246324966</v>
+        <v>79</v>
       </c>
       <c r="C74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="B75">
+        <v>-0.1820048265378515</v>
       </c>
       <c r="C75" t="b">
         <v>1</v>
@@ -2313,18 +2310,21 @@
         <v>1</v>
       </c>
       <c r="E75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>81</v>
+      </c>
+      <c r="B76">
+        <v>-0.2027319592747009</v>
       </c>
       <c r="C76" t="b">
         <v>0</v>
@@ -2333,27 +2333,27 @@
         <v>0</v>
       </c>
       <c r="E76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B77">
-        <v>-0.1820048265378515</v>
+        <v>-0.2189178803002914</v>
       </c>
       <c r="C77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" t="b">
         <v>1</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B78">
-        <v>-0.2027319592747009</v>
+        <v>-0.1414054398988475</v>
       </c>
       <c r="C78" t="b">
         <v>0</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B79">
-        <v>-0.2189178803002914</v>
+        <v>-0.1274662959731365</v>
       </c>
       <c r="C79" t="b">
         <v>0</v>
@@ -2413,10 +2413,10 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B80">
-        <v>-0.1414054398988475</v>
+        <v>-0.2296491298349427</v>
       </c>
       <c r="C80" t="b">
         <v>0</v>
@@ -2425,21 +2425,21 @@
         <v>0</v>
       </c>
       <c r="E80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="b">
         <v>1</v>
       </c>
       <c r="G80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B81">
-        <v>-0.1274662959731365</v>
+        <v>-0.1593555579838632</v>
       </c>
       <c r="C81" t="b">
         <v>0</v>
@@ -2454,21 +2454,21 @@
         <v>1</v>
       </c>
       <c r="G81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B82">
-        <v>-0.2296491298349427</v>
+        <v>-0.1891070006869582</v>
       </c>
       <c r="C82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
@@ -2477,21 +2477,21 @@
         <v>1</v>
       </c>
       <c r="G82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B83">
-        <v>-0.1593555579838632</v>
+        <v>-0.2119195281519203</v>
       </c>
       <c r="C83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="b">
         <v>1</v>
@@ -2500,15 +2500,15 @@
         <v>1</v>
       </c>
       <c r="G83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B84">
-        <v>-0.1891070006869582</v>
+        <v>-0.184285453771279</v>
       </c>
       <c r="C84" t="b">
         <v>1</v>
@@ -2517,7 +2517,7 @@
         <v>1</v>
       </c>
       <c r="E84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="b">
         <v>1</v>
@@ -2528,39 +2528,39 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B85">
-        <v>-0.2119195281519203</v>
+        <v>-0.1389043950286487</v>
       </c>
       <c r="C85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B86">
-        <v>-0.184285453771279</v>
+        <v>-0.194595351118395</v>
       </c>
       <c r="C86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="b">
         <v>1</v>
@@ -2574,33 +2574,30 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B87">
-        <v>-0.1389043950286487</v>
+        <v>-0.2094323762561981</v>
       </c>
       <c r="C87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>91</v>
-      </c>
-      <c r="B88">
-        <v>-0.194595351118395</v>
+        <v>93</v>
       </c>
       <c r="C88" t="b">
         <v>0</v>
@@ -2609,33 +2606,33 @@
         <v>0</v>
       </c>
       <c r="E88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B89">
-        <v>-0.2094323762561981</v>
+        <v>-0.1843566503272119</v>
       </c>
       <c r="C89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="b">
         <v>1</v>
@@ -2643,30 +2640,33 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>95</v>
+      </c>
+      <c r="B90">
+        <v>-0.2064610311547386</v>
       </c>
       <c r="C90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B91">
-        <v>-0.1843566503272119</v>
+        <v>-0.1646599483139209</v>
       </c>
       <c r="C91" t="b">
         <v>0</v>
@@ -2681,15 +2681,15 @@
         <v>0</v>
       </c>
       <c r="G91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B92">
-        <v>-0.2064610311547386</v>
+        <v>-0.1656382046631881</v>
       </c>
       <c r="C92" t="b">
         <v>1</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B93">
-        <v>-0.1707755764195111</v>
+        <v>-0.188146805204511</v>
       </c>
       <c r="C93" t="b">
         <v>0</v>
@@ -2727,38 +2727,38 @@
         <v>0</v>
       </c>
       <c r="G93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B94">
-        <v>-0.1646599483139209</v>
+        <v>-0.2002121226750436</v>
       </c>
       <c r="C94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B95">
-        <v>-0.1656382046631881</v>
+        <v>-0.205184187788136</v>
       </c>
       <c r="C95" t="b">
         <v>1</v>
@@ -2778,16 +2778,16 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B96">
-        <v>-0.188146805204511</v>
+        <v>-0.1845446993087567</v>
       </c>
       <c r="C96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="b">
         <v>0</v>
@@ -2796,15 +2796,15 @@
         <v>0</v>
       </c>
       <c r="G96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B97">
-        <v>-0.2002121226750436</v>
+        <v>-0.199747972224902</v>
       </c>
       <c r="C97" t="b">
         <v>1</v>
@@ -2813,81 +2813,12 @@
         <v>1</v>
       </c>
       <c r="E97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98" t="s">
-        <v>100</v>
-      </c>
-      <c r="B98">
-        <v>-0.205184187788136</v>
-      </c>
-      <c r="C98" t="b">
-        <v>1</v>
-      </c>
-      <c r="D98" t="b">
-        <v>1</v>
-      </c>
-      <c r="E98" t="b">
-        <v>1</v>
-      </c>
-      <c r="F98" t="b">
-        <v>1</v>
-      </c>
-      <c r="G98" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99" t="s">
-        <v>101</v>
-      </c>
-      <c r="B99">
-        <v>-0.1845446993087567</v>
-      </c>
-      <c r="C99" t="b">
-        <v>1</v>
-      </c>
-      <c r="D99" t="b">
-        <v>1</v>
-      </c>
-      <c r="E99" t="b">
-        <v>0</v>
-      </c>
-      <c r="F99" t="b">
-        <v>0</v>
-      </c>
-      <c r="G99" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" t="s">
-        <v>102</v>
-      </c>
-      <c r="B100">
-        <v>-0.199747972224902</v>
-      </c>
-      <c r="C100" t="b">
-        <v>1</v>
-      </c>
-      <c r="D100" t="b">
-        <v>1</v>
-      </c>
-      <c r="E100" t="b">
-        <v>0</v>
-      </c>
-      <c r="F100" t="b">
-        <v>0</v>
-      </c>
-      <c r="G100" t="b">
         <v>0</v>
       </c>
     </row>
